--- a/output_tables/archive/group_summary_old.xlsx
+++ b/output_tables/archive/group_summary_old.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/output_tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/peter_dowty_dnr_wa_gov/Documents/projects/seagrass_restoration_data_2026/output_tables/archive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="8_{59E47FFB-B8F7-45C3-A319-0743BC9995C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AC35531-8A54-4CEE-8F04-3D3E3C8254D6}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{59E47FFB-B8F7-45C3-A319-0743BC9995C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4DC5009-317E-4AAE-B766-D576318D2ABF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="26505" windowHeight="15390" xr2:uid="{DE4F24FA-FBA3-478C-9F9E-E001BBB69A88}"/>
+    <workbookView xWindow="2295" yWindow="90" windowWidth="26505" windowHeight="15390" xr2:uid="{DE4F24FA-FBA3-478C-9F9E-E001BBB69A88}"/>
   </bookViews>
   <sheets>
     <sheet name="group_summary" sheetId="1" r:id="rId1"/>
@@ -1105,7 +1105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1244,6 +1244,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFC000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFFC000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1289,13 +1326,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1390,6 +1430,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1405,6 +1450,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1420,6 +1470,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1435,6 +1490,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1450,6 +1510,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1465,6 +1530,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1482,6 +1552,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1499,6 +1574,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1516,6 +1596,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1533,6 +1618,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1550,6 +1640,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1567,6 +1662,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1585,6 +1685,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -1603,6 +1708,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1621,6 +1731,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-A7F9-4189-9ED9-3B344F10278D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -3239,7 +3354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3284,7 +3399,7 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="6" t="s">
         <v>31</v>
       </c>
       <c r="I19" t="s">
@@ -3316,7 +3431,7 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I20" t="s">
@@ -3348,7 +3463,7 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I21" t="s">
@@ -3380,7 +3495,7 @@
       <c r="D22" t="s">
         <v>11</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="7" t="s">
         <v>34</v>
       </c>
       <c r="I22" t="s">
@@ -3399,7 +3514,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3412,7 +3527,7 @@
       <c r="D23" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
@@ -6300,7 +6415,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6330,7 +6445,7 @@
       <c r="D187" t="s">
         <v>11</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -6347,7 +6462,7 @@
       <c r="D188" t="s">
         <v>11</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="7" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6364,7 +6479,7 @@
       <c r="D189" t="s">
         <v>11</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6381,11 +6496,11 @@
       <c r="D190" t="s">
         <v>11</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6398,7 +6513,7 @@
       <c r="D191" t="s">
         <v>11</v>
       </c>
-      <c r="E191" s="2" t="s">
+      <c r="E191" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F191" t="s">
